--- a/Калькулятор перевода.xlsx
+++ b/Калькулятор перевода.xlsx
@@ -327,7 +327,7 @@
     <t>Калькулятор вывода денег: Россия → Приднестровье → Молдова</t>
   </si>
   <si>
-    <t>Цепочка: ₽ на карте РФ → Юнистрим (комиссия сверху) → ₽ наличными в кассе ПМР → банк покупает ₽ → ПМР-рубль → банк продаёт €/лей/$</t>
+    <t>Цепочка: ₽ на карте РФ → Юнистрим (комиссия сверху) → банк выдачи пересчитывает перевод в ПМР-рубли по своему курсу покупки ₽ → банк обмена продаёт €/лей/$. Наличных рублей РФ на руках не бывает; забрать можно в одном банке, а менять в другом.</t>
   </si>
   <si>
     <t>Заполняй только ЖЁЛТЫЕ ячейки (синий текст). Всё остальное — формулы, считаются сами. Курсы обновляй перед каждым расчётом: где брать — на листе «Источники курсов».</t>
@@ -351,7 +351,7 @@
     <t>Прибанк ПОКУПАЕТ ₽</t>
   </si>
   <si>
-    <t>ПМР-рублей за 1 ₽ — по этому курсу банк забирает твои рубли</t>
+    <t>ПМР-рублей за 1 ₽ — по этому курсу банк выдачи пересчитывает перевод. Обычно это курс покупки ₽ с табло, но называют его в момент выдачи</t>
   </si>
   <si>
     <t>Официальный курс ПРБ для ₽</t>
@@ -411,7 +411,7 @@
     <t>ПМР-рублей на руках</t>
   </si>
   <si>
-    <t>Банк купил твои рубли и выдал ПМР-рубли</t>
+    <t>Столько выдаёт касса банка выдачи. Менять их может уже другой банк</t>
   </si>
   <si>
     <t>Результат</t>
@@ -489,7 +489,7 @@
     <t>Откуда брать курсы</t>
   </si>
   <si>
-    <t>Все три источника проверены 03.09.2026 и отдают данные без регистрации. Курс самого Юнистрима нигде не публикуется — но он и не нужен: Юнистрим выдаёт рубли, не конвертируя.</t>
+    <t>Все три источника проверены 03.09.2026 и отдают данные без регистрации. Курс самого Юнистрима нигде не публикуется — но на этом маршруте он и не нужен: пересчёт делает банк выдачи, по своему курсу.</t>
   </si>
   <si>
     <t>Ячейка на листе «Калькулятор»</t>
@@ -570,7 +570,7 @@
     <t>• Приднестровский рубль не имеет кода ISO 4217 и отсутствует во всех глобальных API курсов. Единственные источники — сайты банков ПМР и ПРБ.</t>
   </si>
   <si>
-    <t>• Юнистрим выдаёт только рубли, доллары и евро — ПМР-рубль он не выдаёт вообще. Конвертация в ПМР-рубль это уже отдельная операция в кассе банка.</t>
+    <t>• Юнистрим выдаёт ПМР-рубли — наличных рублей РФ на руках не бывает. Пересчёт ₽ → ПМР-рубль делает банк выдачи по своему кассовому курсу покупки ₽ (B8); вторую конвертацию делает касса банка обмена (B13). Привязки между ними нет: забрать можно в одном банке, менять в другом.</t>
   </si>
   <si>
     <t>CSV в кодировке windows-1251. Колонки: дата, название, код, номинал, курс. Работает и по http, и по https. Человеку удобнее страница cbpmr.net/kursval.php?lang=ru</t>
